--- a/quotation_template.xlsx
+++ b/quotation_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenseikobayashi/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenseikobayashi/Desktop/report_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B32159D-B2C8-034C-9545-8C93825F18DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26D8D2B-50ED-374F-A97E-E0C7E6C6B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7980" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="見積書" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
   <si>
     <t>発行日：</t>
   </si>
@@ -64,34 +64,19 @@
     <t>画像処理検査機SonicAI one</t>
   </si>
   <si>
-    <t>〒108-0073</t>
-  </si>
-  <si>
     <t>納期：</t>
   </si>
   <si>
     <t>2026年1月末日予定</t>
   </si>
   <si>
-    <t>東京都港区三田3-5-27</t>
-  </si>
-  <si>
     <t>支払い条件：</t>
   </si>
   <si>
     <t>納品後、末締め翌月末支払い（振込）</t>
   </si>
   <si>
-    <t>住友不動産東京三田サウスタワー 10F</t>
-  </si>
-  <si>
     <t>有効期限：</t>
-  </si>
-  <si>
-    <t>TEL：080-8044-3236</t>
-  </si>
-  <si>
-    <t>担当：小林賢正</t>
   </si>
   <si>
     <t>合計金額</t>
@@ -174,526 +159,6 @@
   <si>
     <t>住所：</t>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>納品方法：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>弊社指定の配送業者による配送（軒先渡し）となります。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>送料：本見積に含みます。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>検収条件：製品の納入をもって検収完了（所有権移転）とさせていただきます。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>返品・キャンセル：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>受注生産品のため、ご発注後のキャンセル・返品はお受けできません。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品保証に関して：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Cambria Math"/>
-        <family val="2"/>
-      </rPr>
-      <t>①</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>無償保証期間：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>納品日より</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>年間とします。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　保証範囲（通常運用）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　通常の運用によって故障した場合に限り、無償で修理または交換いたします。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　対応方法：対象部品の送付もしくは技術スタッフの派遣により交換</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　保証の適用除外（有償対応）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　以下の場合は、保証期間内であっても有償対応となります。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　・お客様の故意・過失による破損、落下、水没、改造、分解など。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　・火災、地震、落雷などの天災地変による故障。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　・経年劣化する消耗部品（バッテリー、フィルター等）の交換。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　・指定外の電源電圧や使用環境（高温・多湿等）での使用による故障。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>製品の変更</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>修理が困難な場合、同等機能を持つ代替品への交換とさせていただく場合がございます。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>その他：電源タップ等の配線部材、および</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>等の周辺機器は本見積に含まれません。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>　　　　今回のみ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PoC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>特別値引きを適応します。</t>
-    </r>
-    <phoneticPr fontId="11"/>
-  </si>
 </sst>
 </file>
 
@@ -702,7 +167,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$¥-411]#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -794,26 +259,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="MS Gothic"/>
-      <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Cambria Math"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1057,6 +502,31 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1076,37 +546,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1342,18 +787,13 @@
       <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="2">
-        <f ca="1">TODAY()</f>
-        <v>46100</v>
-      </c>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>2</v>
-      </c>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4"/>
@@ -1368,26 +808,26 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1399,9 +839,7 @@
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
-      <c r="H8" s="5" t="s">
-        <v>6</v>
-      </c>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="1"/>
@@ -1413,201 +851,167 @@
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-      <c r="H10" s="7" t="s">
-        <v>9</v>
-      </c>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C11" s="3"/>
       <c r="D11" s="3"/>
-      <c r="H11" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-      <c r="H12" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="8">
-        <v>46022</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C13" s="8"/>
       <c r="D13" s="3"/>
-      <c r="H13" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H14" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="40">
         <f>I28</f>
-        <v>1998000</v>
-      </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="28" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="43" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="24"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="29"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="32"/>
+      <c r="B18" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="30"/>
       <c r="H18" s="10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="11">
-        <v>1</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="13">
-        <v>2498000</v>
-      </c>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="13"/>
       <c r="I19" s="13">
         <f t="shared" ref="I19:I20" si="0">F19*H19</f>
-        <v>2498000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="11">
-        <v>1</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="13">
-        <v>-500000</v>
-      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="13"/>
       <c r="I20" s="13">
         <f t="shared" si="0"/>
-        <v>-500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="34"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="34"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="32"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="13"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="34"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="34"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="34"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="32"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="34"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="13"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="34"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="11"/>
       <c r="G27" s="12"/>
       <c r="H27" s="13"/>
@@ -1615,29 +1019,29 @@
     </row>
     <row r="28" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H28" s="15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I28" s="13">
         <f>SUM(I19:I27)</f>
-        <v>1998000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H29" s="15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I29" s="13">
         <f>I28*0.1</f>
-        <v>199800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H30" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I30" s="13">
         <f>I28+I29</f>
-        <v>2197800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1651,148 +1055,146 @@
       <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="32"/>
+      <c r="B32" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="40" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="42"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="21"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="43"/>
-      <c r="C34" s="44"/>
-      <c r="D34" s="44"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="44"/>
-      <c r="G34" s="44"/>
-      <c r="H34" s="44"/>
-      <c r="I34" s="45"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="23"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="24"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="43"/>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-      <c r="I35" s="45"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="23"/>
+      <c r="I35" s="24"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="43"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-      <c r="I36" s="45"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="24"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="43"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="45"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="24"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="43"/>
-      <c r="C38" s="44"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="45"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="24"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="43"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="45"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="24"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="43"/>
-      <c r="C40" s="44"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-      <c r="I40" s="45"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
+      <c r="G40" s="23"/>
+      <c r="H40" s="23"/>
+      <c r="I40" s="24"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="43"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="45"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="23"/>
+      <c r="I41" s="24"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="43"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="24"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="43"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="45"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="24"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="43"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="45"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="23"/>
+      <c r="I44" s="24"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="46"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="48"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="27"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
@@ -1816,6 +1218,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B33:I45"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
@@ -1824,16 +1236,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -1862,7 +1264,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -1887,28 +1289,28 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="A4" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1916,15 +1318,15 @@
     <row r="7" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="H8" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -1942,25 +1344,25 @@
       </c>
       <c r="D10" s="3"/>
       <c r="H10" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="3"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3"/>
       <c r="H12" s="7"/>
@@ -1975,56 +1377,56 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="40">
         <f>I28</f>
         <v>1998000</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="28" t="s">
-        <v>20</v>
+      <c r="D15" s="41"/>
+      <c r="E15" s="43" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="24"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="29"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="32"/>
+      <c r="B18" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="30"/>
       <c r="H18" s="10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
+      <c r="B19" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="11">
         <v>1</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H19" s="13">
         <v>2498000</v>
@@ -2035,17 +1437,17 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
+      <c r="B20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="11">
         <v>1</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H20" s="13">
         <v>-500000</v>
@@ -2056,70 +1458,70 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="34"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="34"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="32"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="13"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="34"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="34"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="34"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="32"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="34"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="13"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="34"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="11"/>
       <c r="G27" s="12"/>
       <c r="H27" s="13"/>
@@ -2127,7 +1529,7 @@
     </row>
     <row r="28" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H28" s="15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I28" s="13">
         <f>SUM(I19:I27)</f>
@@ -2136,7 +1538,7 @@
     </row>
     <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H29" s="15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I29" s="13">
         <f>I28*0.1</f>
@@ -2145,7 +1547,7 @@
     </row>
     <row r="30" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H30" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I30" s="13">
         <f>I28+I29</f>
@@ -2163,148 +1565,148 @@
       <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="32"/>
+      <c r="B32" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="37"/>
+      <c r="B33" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="46"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="38"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="39"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="48"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="38"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="39"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="48"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="38"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="39"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="38"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="39"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="48"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="38"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="39"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="48"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="38"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="39"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="48"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="38"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="39"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="48"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="38"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="39"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="48"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="38"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="39"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="48"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="38"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="39"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="48"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="38"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="39"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="48"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="27"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="29"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="44"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
@@ -2328,6 +1730,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B33:I45"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
@@ -2336,16 +1748,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
@@ -2374,7 +1776,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="H1" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -2399,28 +1801,28 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
+      <c r="A4" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
@@ -2428,15 +1830,15 @@
     <row r="7" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="8" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="H8" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J8" s="18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="6" customHeight="1" x14ac:dyDescent="0.2">
@@ -2454,25 +1856,25 @@
       </c>
       <c r="D10" s="3"/>
       <c r="H10" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="D11" s="3"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="3"/>
       <c r="H12" s="7"/>
@@ -2487,56 +1889,56 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="25">
+      <c r="B15" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="40">
         <f>I28</f>
         <v>1998000</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="28" t="s">
-        <v>20</v>
+      <c r="D15" s="41"/>
+      <c r="E15" s="43" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="24"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="29"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="44"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="32"/>
+      <c r="B18" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G18" s="30"/>
       <c r="H18" s="10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
+      <c r="B19" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="30"/>
       <c r="F19" s="11">
         <v>1</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H19" s="13">
         <v>2498000</v>
@@ -2547,17 +1949,17 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
+      <c r="B20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="30"/>
       <c r="F20" s="11">
         <v>1</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H20" s="13">
         <v>-500000</v>
@@ -2568,70 +1970,70 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="34"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="30"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="34"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="32"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="13"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="34"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="34"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="30"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="34"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="32"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="30"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="34"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="13"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="34"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="11"/>
       <c r="G27" s="12"/>
       <c r="H27" s="13"/>
@@ -2639,7 +2041,7 @@
     </row>
     <row r="28" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H28" s="15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I28" s="13">
         <f>SUM(I19:I27)</f>
@@ -2648,7 +2050,7 @@
     </row>
     <row r="29" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H29" s="15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I29" s="13">
         <f>I28*0.1</f>
@@ -2657,7 +2059,7 @@
     </row>
     <row r="30" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H30" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I30" s="13">
         <f>I28+I29</f>
@@ -2675,148 +2077,148 @@
       <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="32"/>
+      <c r="B32" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="30"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="26"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="37"/>
+      <c r="B33" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="46"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="38"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="39"/>
+      <c r="B34" s="47"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="48"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="38"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="39"/>
+      <c r="B35" s="47"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="48"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="38"/>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="39"/>
+      <c r="B36" s="47"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="48"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="38"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="39"/>
+      <c r="B37" s="47"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="48"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="38"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="39"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="35"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="48"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="38"/>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="20"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="39"/>
+      <c r="B39" s="47"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="48"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="38"/>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="39"/>
+      <c r="B40" s="47"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="48"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="38"/>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="39"/>
+      <c r="B41" s="47"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="48"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="38"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="39"/>
+      <c r="B42" s="47"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="48"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="38"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="39"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="48"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="38"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="39"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="48"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="27"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="29"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="37"/>
+      <c r="I45" s="44"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
@@ -2840,6 +2242,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B33:I45"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
@@ -2848,16 +2260,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1" gridLines="1"/>

--- a/quotation_template.xlsx
+++ b/quotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenseikobayashi/Desktop/report_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26D8D2B-50ED-374F-A97E-E0C7E6C6B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EDDF5BA-39CE-FA4F-B508-C5EBBDC3DF9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="見積書" sheetId="1" r:id="rId1"/>
@@ -250,24 +250,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Arial (本文)"/>
+      <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="9"/>
+      <name val="Arial (本文)"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Arial (本文)"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="5">
@@ -466,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -502,6 +502,11 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -513,9 +518,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -552,6 +555,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -808,26 +814,26 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
@@ -883,37 +889,37 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="43">
         <f>I28</f>
         <v>0</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="43" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="46" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="47"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="32" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
@@ -922,106 +928,106 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13">
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21">
         <f t="shared" ref="I19:I20" si="0">F19*H19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13">
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="20"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="14"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="20"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="20"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="20"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="14"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="20"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="20"/>
     </row>
     <row r="28" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H28" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="21">
         <f>SUM(I19:I27)</f>
         <v>0</v>
       </c>
@@ -1030,7 +1036,7 @@
       <c r="H29" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="21">
         <f>I28*0.1</f>
         <v>0</v>
       </c>
@@ -1039,7 +1045,7 @@
       <c r="H30" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="21">
         <f>I28+I29</f>
         <v>0</v>
       </c>
@@ -1055,146 +1061,146 @@
       <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="19"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="21"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="24"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="22"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="24"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="27"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="22"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="24"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="27"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="24"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="27"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="24"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="27"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="22"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="24"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="27"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="22"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="24"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="27"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="22"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="23"/>
-      <c r="H40" s="23"/>
-      <c r="I40" s="24"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="27"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="22"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="24"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="27"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="22"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="24"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="27"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="22"/>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
-      <c r="F43" s="23"/>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-      <c r="I43" s="24"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="27"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="22"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="24"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="27"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="27"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="30"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
@@ -1289,28 +1295,28 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1377,37 +1383,37 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="43">
         <f>I28</f>
         <v>1998000</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="43" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="46" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="47"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="32" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
@@ -1416,12 +1422,12 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="11">
         <v>1</v>
       </c>
@@ -1437,12 +1443,12 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="11">
         <v>1</v>
       </c>
@@ -1458,70 +1464,70 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="13"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="13"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="11"/>
       <c r="G27" s="12"/>
       <c r="H27" s="13"/>
@@ -1565,148 +1571,148 @@
       <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="46"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="49"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="47"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="48"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="51"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="47"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="48"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="47"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="47"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="48"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="51"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="47"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="48"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="51"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="47"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="48"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="51"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="47"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="48"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="51"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="47"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="48"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="51"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="47"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="48"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="51"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="47"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="48"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="51"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="47"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="48"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="51"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="42"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="44"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="47"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
@@ -1801,28 +1807,28 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="6" t="s">
         <v>4</v>
       </c>
@@ -1889,37 +1895,37 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="43">
         <f>I28</f>
         <v>1998000</v>
       </c>
-      <c r="D15" s="41"/>
-      <c r="E15" s="43" t="s">
+      <c r="D15" s="44"/>
+      <c r="E15" s="46" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="39"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="44"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="47"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="32" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G18" s="30"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="10" t="s">
         <v>18</v>
       </c>
@@ -1928,12 +1934,12 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
       <c r="F19" s="11">
         <v>1</v>
       </c>
@@ -1949,12 +1955,12 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="33"/>
       <c r="F20" s="11">
         <v>1</v>
       </c>
@@ -1970,70 +1976,70 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="30"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
       <c r="F21" s="11"/>
       <c r="G21" s="12"/>
       <c r="H21" s="13"/>
       <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="30"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12"/>
       <c r="H22" s="13"/>
       <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="28"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="30"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12"/>
       <c r="H23" s="13"/>
       <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="28"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="30"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
       <c r="H24" s="13"/>
       <c r="I24" s="14"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="30"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12"/>
       <c r="H25" s="13"/>
       <c r="I25" s="14"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="28"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="30"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12"/>
       <c r="H26" s="13"/>
       <c r="I26" s="14"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="30"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
       <c r="F27" s="11"/>
       <c r="G27" s="12"/>
       <c r="H27" s="13"/>
@@ -2077,148 +2083,148 @@
       <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="46"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="49"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="47"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="35"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="48"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="38"/>
+      <c r="D34" s="38"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="51"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="47"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="35"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="48"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="38"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="51"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="47"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="35"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="48"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="38"/>
+      <c r="D36" s="38"/>
+      <c r="E36" s="38"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="51"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="47"/>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="48"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="38"/>
+      <c r="D37" s="38"/>
+      <c r="E37" s="38"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="38"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="51"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="47"/>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="48"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="51"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="47"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="48"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="38"/>
+      <c r="E39" s="38"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="38"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="51"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="47"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="48"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="51"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="47"/>
-      <c r="C41" s="35"/>
-      <c r="D41" s="35"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="48"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="38"/>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="51"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="47"/>
-      <c r="C42" s="35"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="48"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="38"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="51"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="47"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="48"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="51"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="47"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="48"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="51"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="42"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="44"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="40"/>
+      <c r="E45" s="40"/>
+      <c r="F45" s="40"/>
+      <c r="G45" s="40"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="47"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>

--- a/quotation_template.xlsx
+++ b/quotation_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenseikobayashi/Desktop/report_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632CF401-240F-7047-B95A-FE4C6CAE326A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14441077-CFAB-3A48-924E-056AE813914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12220" yWindow="1940" windowWidth="29400" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="見積書" sheetId="1" r:id="rId1"/>
@@ -1010,6 +1010,29 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1029,37 +1052,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1366,26 +1366,26 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
       <c r="E6" s="6" t="s">
         <v>3</v>
       </c>
@@ -1441,37 +1441,37 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="42">
         <f>I28</f>
         <v>0</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="30" t="s">
+      <c r="D15" s="43"/>
+      <c r="E15" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="26"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="31"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="46"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35" t="s">
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="34"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="10" t="s">
         <v>17</v>
       </c>
@@ -1480,10 +1480,10 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="36"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="32"/>
       <c r="F19" s="18"/>
       <c r="G19" s="19"/>
       <c r="H19" s="20"/>
@@ -1493,10 +1493,10 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="36"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="18"/>
       <c r="G20" s="19"/>
       <c r="H20" s="20"/>
@@ -1506,70 +1506,70 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="36"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
       <c r="F21" s="18"/>
       <c r="G21" s="19"/>
       <c r="H21" s="20"/>
       <c r="I21" s="19"/>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="36"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="18"/>
       <c r="G22" s="19"/>
       <c r="H22" s="20"/>
       <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="36"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
       <c r="F23" s="18"/>
       <c r="G23" s="19"/>
       <c r="H23" s="20"/>
       <c r="I23" s="19"/>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="36"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
       <c r="F24" s="18"/>
       <c r="G24" s="19"/>
       <c r="H24" s="20"/>
       <c r="I24" s="19"/>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="36"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="34"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="32"/>
       <c r="F25" s="18"/>
       <c r="G25" s="19"/>
       <c r="H25" s="20"/>
       <c r="I25" s="19"/>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="36"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="34"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="32"/>
       <c r="F26" s="18"/>
       <c r="G26" s="19"/>
       <c r="H26" s="20"/>
       <c r="I26" s="19"/>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="36"/>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="34"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
       <c r="H27" s="20"/>
@@ -1613,146 +1613,146 @@
       <c r="I31" s="15"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="32"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="40"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="23"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="41"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="43"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="26"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="41"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="43"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="26"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="41"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="43"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="26"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="41"/>
-      <c r="C37" s="42"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="43"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="41"/>
-      <c r="C38" s="42"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="43"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="25"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="26"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="41"/>
-      <c r="C39" s="42"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="43"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="26"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="41"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="43"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="26"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="41"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="43"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="26"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="41"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="42"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="43"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="25"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="26"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B43" s="41"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="43"/>
+      <c r="B43" s="24"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="26"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B44" s="41"/>
-      <c r="C44" s="42"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="43"/>
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="26"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="44"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="46"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="29"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="16"/>
@@ -1776,6 +1776,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B33:I45"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
@@ -1784,19 +1794,9 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
-  <printOptions horizontalCentered="1" gridLines="1"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="83" fitToWidth="0" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
   <drawing r:id="rId1"/>
@@ -1849,28 +1849,28 @@
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="37"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
       <c r="E6" s="6" t="s">
         <v>3</v>
       </c>
@@ -1937,37 +1937,37 @@
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="42">
         <f>見積書!C15</f>
         <v>0</v>
       </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="30" t="s">
+      <c r="D15" s="43"/>
+      <c r="E15" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="26"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="31"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="46"/>
     </row>
     <row r="17" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="18" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="9"/>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="35" t="s">
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="34"/>
+      <c r="G18" s="32"/>
       <c r="H18" s="10" t="s">
         <v>17</v>
       </c>
@@ -1976,13 +1976,13 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="47">
+      <c r="B19" s="51">
         <f>見積書!B19</f>
         <v>0</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="34"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="32"/>
       <c r="F19" s="11">
         <f>見積書!F19</f>
         <v>0</v>
@@ -2001,13 +2001,13 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="47">
+      <c r="B20" s="51">
         <f>見積書!B20</f>
         <v>0</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="34"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
       <c r="F20" s="11">
         <f>見積書!F20</f>
         <v>0</v>
@@ -2026,13 +2026,13 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="47">
+      <c r="B21" s="51">
         <f>見積書!B21</f>
         <v>0</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="34"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="32"/>
       <c r="F21" s="11">
         <f>見積書!F21</f>
         <v>0</v>
@@ -2051,13 +2051,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="47">
+      <c r="B22" s="51">
         <f>見積書!B22</f>
         <v>0</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="34"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="11">
         <f>見積書!F22</f>
         <v>0</v>
@@ -2076,13 +2076,13 @@
       </c>
     </row>
     <row r="23" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="47">
+      <c r="B23" s="51">
         <f>見積書!B23</f>
         <v>0</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="34"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="32"/>
       <c r="F23" s="11">
         <f>見積書!F23</f>
         <v>0</v>
@@ -2101,13 +2101,13 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="47">
+      <c r="B24" s="51">
         <f>見積書!B24</f>
         <v>0</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="32"/>
       <c r="F24" s="11">
         <f>見積書!F24</f>
         <v>0</v>
@@ -2126,13 +2126,13 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="47">
+      <c r="B25" s="51">
         <f>見積書!B25</f>
         <v>0</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="34"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="32"/>
       <c r="F25" s="11">
         <f>見積書!F25</f>
         <v>0</v>
@@ -2151,13 +2151,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="47">
+      <c r="B26" s="51">
         <f>見積書!B26</f>
         <v>0</v>
       </c>
-      <c r="C26" s="33"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="34"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="32"/>
       <c r="F26" s="11">
         <f>見積書!F26</f>
         <v>0</v>
@@ -2176,13 +2176,13 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="47">
+      <c r="B27" s="51">
         <f>見積書!B27</f>
         <v>0</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="34"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="32"/>
       <c r="F27" s="11">
         <f>見積書!F27</f>
         <v>0</v>
@@ -2238,148 +2238,148 @@
       <c r="I31" s="15"/>
     </row>
     <row r="32" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C32" s="33"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="32"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
       <c r="I33" s="48"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="49"/>
-      <c r="C34" s="22"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
       <c r="I34" s="50"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="49"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
       <c r="I35" s="50"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="49"/>
-      <c r="C36" s="22"/>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
       <c r="I36" s="50"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="49"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="37"/>
       <c r="I37" s="50"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="49"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="22"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="37"/>
       <c r="I38" s="50"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="49"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
       <c r="I39" s="50"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="49"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="22"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="22"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
       <c r="I40" s="50"/>
     </row>
     <row r="41" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="49"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="22"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
       <c r="I41" s="50"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="49"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="22"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
       <c r="I42" s="50"/>
     </row>
     <row r="43" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B43" s="49"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
       <c r="I43" s="50"/>
     </row>
     <row r="44" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B44" s="49"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
       <c r="I44" s="50"/>
     </row>
     <row r="45" spans="2:9" ht="13" x14ac:dyDescent="0.15">
-      <c r="B45" s="29"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="24"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="31"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+      <c r="E45" s="39"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="39"/>
+      <c r="H45" s="39"/>
+      <c r="I45" s="46"/>
     </row>
     <row r="46" spans="2:9" ht="13" x14ac:dyDescent="0.15">
       <c r="B46" s="16"/>
@@ -2403,6 +2403,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="B33:I45"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
@@ -2411,16 +2421,6 @@
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B32:I32"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:D16"/>
-    <mergeCell ref="E15:E16"/>
   </mergeCells>
   <phoneticPr fontId="11"/>
   <printOptions horizontalCentered="1" gridLines="1"/>
